--- a/data/music.xlsx
+++ b/data/music.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindanakasone/Documents/GitHub/playlist-visualized/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDAE0F-0EC7-6F41-B4CD-1C1BA22EC1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AF0D03-1F5B-F041-804F-AED4E77CE14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="7680" windowWidth="29400" windowHeight="16360" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
   </bookViews>
